--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008452553723509622</v>
       </c>
       <c r="C2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>47924042</v>
+        <v>3962213</v>
       </c>
       <c r="L2" t="n">
-        <v>25428396</v>
+        <v>1700776</v>
       </c>
       <c r="M2" t="n">
-        <v>5846692</v>
+        <v>308109</v>
       </c>
       <c r="N2" t="n">
-        <v>271519</v>
+        <v>6444</v>
       </c>
       <c r="O2" t="n">
-        <v>3439013</v>
+        <v>170174</v>
       </c>
       <c r="P2" t="n">
-        <v>1211747</v>
+        <v>644</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999881386756897</v>
+        <v>0.9999905228614807</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8356173038482666</v>
+        <v>0.7214266657829285</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7013431787490845</v>
+        <v>0.5298144817352295</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6339237689971924</v>
+        <v>0.4011914432048798</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2037649154663086</v>
+        <v>0.03815930336713791</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6716128587722778</v>
+        <v>0.3969248831272125</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8184399604797363</v>
+        <v>0.3910139501094818</v>
       </c>
       <c r="X2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559435248374939</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116207361221313</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580287098884583</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615698337554932</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901967465877533</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002025028638077513</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>47924042</v>
+        <v>3962213</v>
       </c>
       <c r="E3" t="n">
-        <v>7247292</v>
+        <v>974991</v>
       </c>
       <c r="F3" t="n">
-        <v>223862</v>
+        <v>43530</v>
       </c>
       <c r="G3" t="n">
-        <v>24665</v>
+        <v>4453</v>
       </c>
       <c r="H3" t="n">
-        <v>14015</v>
+        <v>3469</v>
       </c>
       <c r="I3" t="n">
-        <v>642</v>
+        <v>45</v>
       </c>
       <c r="J3" t="n">
-        <v>110764990</v>
+        <v>10069560</v>
       </c>
       <c r="K3" t="n">
-        <v>115713802</v>
+        <v>9897308</v>
       </c>
       <c r="L3" t="n">
-        <v>133454461</v>
+        <v>11566735</v>
       </c>
       <c r="M3" t="n">
-        <v>166889813</v>
+        <v>15011741</v>
       </c>
       <c r="N3" t="n">
-        <v>178529553</v>
+        <v>16163466</v>
       </c>
       <c r="O3" t="n">
-        <v>173280325</v>
+        <v>15644865</v>
       </c>
       <c r="P3" t="n">
-        <v>178178645</v>
+        <v>16221065</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8645153641700745</v>
+        <v>0.7942353487014771</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7006375193595886</v>
+        <v>0.5092287063598633</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5670972466468811</v>
+        <v>0.326254278421402</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2755265235900879</v>
+        <v>0.07151497900485992</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6125606894493103</v>
+        <v>0.3319962918758392</v>
       </c>
       <c r="W3" t="n">
-        <v>0.569284200668335</v>
+        <v>0.003320751711726189</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2185497</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93996</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75314</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110765820</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122695174</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141081682</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>168804129</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179257373</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174411852</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178301599</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575085639953613</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097797274589539</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570374250411987</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609038710594177</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013426303863525</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03196808737360584</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8698800</v>
+        <v>1367596</v>
       </c>
       <c r="E4" t="n">
-        <v>25428396</v>
+        <v>1700776</v>
       </c>
       <c r="F4" t="n">
-        <v>1804634</v>
+        <v>212680</v>
       </c>
       <c r="G4" t="n">
-        <v>152001</v>
+        <v>25790</v>
       </c>
       <c r="H4" t="n">
-        <v>195765</v>
+        <v>32835</v>
       </c>
       <c r="I4" t="n">
-        <v>13582</v>
+        <v>221</v>
       </c>
       <c r="J4" t="n">
-        <v>830</v>
+        <v>60</v>
       </c>
       <c r="K4" t="n">
-        <v>9427621</v>
+        <v>1529978</v>
       </c>
       <c r="L4" t="n">
-        <v>10828313</v>
+        <v>1509359</v>
       </c>
       <c r="M4" t="n">
-        <v>3376329</v>
+        <v>459876</v>
       </c>
       <c r="N4" t="n">
-        <v>1060992</v>
+        <v>162427</v>
       </c>
       <c r="O4" t="n">
-        <v>1681516</v>
+        <v>258557</v>
       </c>
       <c r="P4" t="n">
-        <v>268810</v>
+        <v>1003</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999940991401672</v>
+        <v>0.9999952912330627</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8498207926750183</v>
+        <v>0.7560822367668152</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7009902000427246</v>
+        <v>0.519317626953125</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5986513495445251</v>
+        <v>0.3598630726337433</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2342734932899475</v>
+        <v>0.04976484552025795</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6407290697097778</v>
+        <v>0.361568808555603</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6714950203895569</v>
+        <v>0.006585574708878994</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2284621</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>915390</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61077</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12548</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2446249</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3201092</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1462013</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>333172</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549989</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567253589630127</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106993675231934</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575327396392822</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612366437911987</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016548991203308</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>522942</v>
+        <v>120450</v>
       </c>
       <c r="E5" t="n">
-        <v>2896404</v>
+        <v>397298</v>
       </c>
       <c r="F5" t="n">
-        <v>5846692</v>
+        <v>308109</v>
       </c>
       <c r="G5" t="n">
-        <v>324801</v>
+        <v>41874</v>
       </c>
       <c r="H5" t="n">
-        <v>665934</v>
+        <v>76353</v>
       </c>
       <c r="I5" t="n">
-        <v>53006</v>
+        <v>289</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7510535</v>
+        <v>1026501</v>
       </c>
       <c r="L5" t="n">
-        <v>10864830</v>
+        <v>1639130</v>
       </c>
       <c r="M5" t="n">
-        <v>4463166</v>
+        <v>636274</v>
       </c>
       <c r="N5" t="n">
-        <v>713936</v>
+        <v>83663</v>
       </c>
       <c r="O5" t="n">
-        <v>2175146</v>
+        <v>342404</v>
       </c>
       <c r="P5" t="n">
-        <v>916798</v>
+        <v>193288</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999954104423523</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9061992764472961</v>
+        <v>0.8442690372467041</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8798669576644897</v>
+        <v>0.8082060813903809</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9565861821174622</v>
+        <v>0.9332267045974731</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9901707172393799</v>
+        <v>0.9850091338157654</v>
       </c>
       <c r="V5" t="n">
-        <v>0.978642463684082</v>
+        <v>0.9633917808532715</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9934343099594116</v>
+        <v>0.9881645441055298</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89118</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>946597</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109931</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321315</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2355496</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3274384</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1473924</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>334164</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553878</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734087586402893</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641398787498474</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983741283416748</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963043928146362</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938869476318359</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983808398246765</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>152981</v>
+        <v>22413</v>
       </c>
       <c r="E6" t="n">
-        <v>208210</v>
+        <v>27606</v>
       </c>
       <c r="F6" t="n">
-        <v>252133</v>
+        <v>25598</v>
       </c>
       <c r="G6" t="n">
-        <v>271519</v>
+        <v>6444</v>
       </c>
       <c r="H6" t="n">
-        <v>91941</v>
+        <v>7937</v>
       </c>
       <c r="I6" t="n">
-        <v>8548</v>
+        <v>101</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71955</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59191</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120711</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77015</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>49961</v>
+        <v>18045</v>
       </c>
       <c r="E7" t="n">
-        <v>433280</v>
+        <v>97413</v>
       </c>
       <c r="F7" t="n">
-        <v>1006410</v>
+        <v>154198</v>
       </c>
       <c r="G7" t="n">
-        <v>492265</v>
+        <v>72389</v>
       </c>
       <c r="H7" t="n">
-        <v>3439013</v>
+        <v>170174</v>
       </c>
       <c r="I7" t="n">
-        <v>193032</v>
+        <v>347</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8916</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328269</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83923</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>323</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>2937</v>
+        <v>1474</v>
       </c>
       <c r="E8" t="n">
-        <v>43127</v>
+        <v>12051</v>
       </c>
       <c r="F8" t="n">
-        <v>89290</v>
+        <v>23870</v>
       </c>
       <c r="G8" t="n">
-        <v>67260</v>
+        <v>17921</v>
       </c>
       <c r="H8" t="n">
-        <v>713861</v>
+        <v>137963</v>
       </c>
       <c r="I8" t="n">
-        <v>1211747</v>
+        <v>644</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
